--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -41853,12 +41853,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -41892,81 +41892,95 @@
         </is>
       </c>
       <c r="N238" t="n">
+        <v>4</v>
+      </c>
+      <c r="O238" t="n">
+        <v>4</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT238" t="n">
         <v>1</v>
       </c>
-      <c r="O238" t="n">
-        <v>1</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO238" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP238" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
-      <c r="AT238" t="n">
-        <v>0</v>
-      </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -41993,17 +42007,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42028,7 +42042,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -42037,81 +42051,170 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42143,12 +42246,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42173,7 +42276,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -42182,93 +42285,81 @@
         </is>
       </c>
       <c r="N240" t="n">
+        <v>1</v>
+      </c>
+      <c r="O240" t="n">
+        <v>1</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="n">
         <v>0</v>
       </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
-      <c r="AT240" t="n">
-        <v>2</v>
-      </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42295,17 +42386,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -42344,168 +42435,76 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="P241" t="n">
+      <c r="R241" t="n">
         <v>0</v>
       </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42537,12 +42536,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -42567,7 +42566,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -42576,81 +42575,93 @@
         </is>
       </c>
       <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT242" t="n">
         <v>2</v>
       </c>
-      <c r="O242" t="n">
-        <v>2</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO242" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP242" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
-      <c r="AT242" t="n">
-        <v>0</v>
-      </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -42677,7 +42688,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -42712,7 +42723,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -42721,26 +42732,106 @@
         </is>
       </c>
       <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN243" t="b">
         <v>1</v>
-      </c>
-      <c r="O243" t="n">
-        <v>1</v>
-      </c>
-      <c r="P243" t="n">
-        <v>1</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -42834,17 +42925,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -42878,173 +42969,81 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
-      </c>
-      <c r="P244" t="n">
-        <v>1</v>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43076,12 +43075,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43106,7 +43105,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -43115,81 +43114,93 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P245" t="n">
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43216,7 +43227,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -43251,7 +43262,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -43260,26 +43271,106 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
@@ -43373,17 +43464,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -43422,168 +43513,76 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="P247" t="n">
+      <c r="R247" t="n">
         <v>0</v>
       </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ247" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43615,12 +43614,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43645,7 +43644,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -43654,81 +43653,93 @@
         </is>
       </c>
       <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
         <v>2</v>
       </c>
-      <c r="O248" t="n">
-        <v>2</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO248" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP248" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
-      <c r="AT248" t="n">
-        <v>0</v>
-      </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43755,17 +43766,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43790,7 +43801,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -43804,76 +43815,168 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="R249" t="n">
+      <c r="P249" t="n">
         <v>0</v>
       </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN249" t="b">
+        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43905,12 +44008,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43935,7 +44038,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -43944,93 +44047,81 @@
         </is>
       </c>
       <c r="N250" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" t="n">
+        <v>2</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
+      <c r="AT250" t="n">
         <v>0</v>
       </c>
-      <c r="O250" t="n">
-        <v>0</v>
-      </c>
-      <c r="P250" t="n">
-        <v>0</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP250" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
-      <c r="AT250" t="n">
-        <v>2</v>
-      </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44057,17 +44148,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44106,168 +44197,76 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="P251" t="n">
+      <c r="R251" t="n">
         <v>0</v>
       </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44299,12 +44298,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44329,7 +44328,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -44338,81 +44337,93 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
         <v>2</v>
       </c>
-      <c r="O252" t="n">
-        <v>2</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO252" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP252" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
-      <c r="AT252" t="n">
-        <v>0</v>
-      </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44439,17 +44450,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44474,90 +44485,182 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N253" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
         <v>1</v>
       </c>
-      <c r="O253" t="n">
-        <v>1</v>
-      </c>
-      <c r="R253" t="n">
-        <v>0.00367281181951979</v>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44589,12 +44692,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44619,104 +44722,90 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N254" t="n">
+        <v>2</v>
+      </c>
+      <c r="O254" t="n">
+        <v>2</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
+      <c r="AT254" t="n">
         <v>0</v>
       </c>
-      <c r="O254" t="n">
-        <v>0</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP254" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT254" t="n">
-        <v>1</v>
-      </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44743,17 +44832,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44787,170 +44876,81 @@
         </is>
       </c>
       <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="n">
+        <v>1</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="n">
         <v>0</v>
       </c>
-      <c r="O255" t="n">
-        <v>0</v>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO255" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP255" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT255" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU255" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV255" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -44982,12 +44982,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45034,68 +45034,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45122,17 +45136,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45171,17 +45185,34 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="R257" t="n">
-        <v>0</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -45189,6 +45220,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45201,12 +45290,12 @@
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
       <c r="AT257" t="n">
@@ -45214,47 +45303,47 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45281,17 +45370,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45330,163 +45419,467 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="V258" t="inlineStr">
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="W258" t="inlineStr">
+      <c r="AT259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X258" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>Tyfoidfeber</t>
         </is>
       </c>
-      <c r="Y258" t="inlineStr">
+      <c r="Y260" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr">
+      <c r="Z260" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA258" t="inlineStr">
+      <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB258" t="inlineStr">
+      <c r="AB260" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC258" t="inlineStr">
+      <c r="AC260" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD258" t="inlineStr">
+      <c r="AD260" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE258" t="inlineStr">
+      <c r="AE260" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF258" t="inlineStr">
+      <c r="AF260" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG258" t="inlineStr">
+      <c r="AG260" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH258" t="inlineStr">
+      <c r="AH260" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI258" t="inlineStr">
+      <c r="AI260" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ258" t="inlineStr">
+      <c r="AJ260" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK258" t="inlineStr">
+      <c r="AK260" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
         </is>
       </c>
-      <c r="AM258" t="inlineStr">
+      <c r="AM260" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN258" t="b">
+      <c r="AN260" t="b">
         <v>1</v>
       </c>
-      <c r="AO258" t="inlineStr">
+      <c r="AO260" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP258" t="inlineStr">
+      <c r="AP260" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ258" t="inlineStr">
+      <c r="AQ260" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS258" t="inlineStr">
+      <c r="AS260" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="AT258" t="n">
+      <c r="AT260" t="n">
         <v>1</v>
       </c>
-      <c r="AU258" t="inlineStr">
+      <c r="AU260" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV258" t="inlineStr">
+      <c r="AV260" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW258" t="inlineStr">
+      <c r="AW260" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX258" t="inlineStr">
+      <c r="AX260" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY258" t="inlineStr">
+      <c r="AY260" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ258" t="inlineStr">
+      <c r="AZ260" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA258" t="inlineStr">
+      <c r="BA260" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB258" t="inlineStr">
+      <c r="BB260" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC258" t="inlineStr">
+      <c r="BC260" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -45608,7 +46001,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -45618,7 +46011,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -45638,7 +46031,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -45670,7 +46063,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -39964,13 +39964,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O226" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R226" t="n">
-        <v>0.02203687091711874</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -40961,13 +40961,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R233" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -41120,10 +41120,10 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
@@ -41354,13 +41354,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R235" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -44837,12 +44837,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44867,12 +44867,12 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N255" t="n">
@@ -44882,7 +44882,7 @@
         <v>1</v>
       </c>
       <c r="R255" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -44915,42 +44915,42 @@
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44982,12 +44982,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45021,95 +45021,81 @@
         </is>
       </c>
       <c r="N256" t="n">
+        <v>1</v>
+      </c>
+      <c r="O256" t="n">
+        <v>1</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="n">
         <v>0</v>
       </c>
-      <c r="O256" t="n">
-        <v>0</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP256" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT256" t="n">
-        <v>1</v>
-      </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -45136,7 +45122,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -45185,98 +45171,23 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U257" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -45370,17 +45281,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45419,76 +45330,165 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="R258" t="n">
-        <v>0</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45520,12 +45520,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45572,82 +45572,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -45674,7 +45660,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -45723,98 +45709,23 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U260" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
@@ -45880,6 +45791,240 @@
         </is>
       </c>
       <c r="BC260" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -46001,7 +46146,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -46011,7 +46156,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -46063,7 +46208,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -39964,13 +39964,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O226" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R226" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.03305530637567811</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -41354,13 +41354,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R235" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -44982,12 +44982,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45012,12 +45012,12 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N256" t="n">
@@ -45026,76 +45026,88 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
+      <c r="P256" t="n">
+        <v>1</v>
+      </c>
       <c r="R256" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45122,17 +45134,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45157,37 +45169,115 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O257" t="n">
-        <v>0</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P257" t="n">
+        <v>1</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -45196,65 +45286,65 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
         </is>
       </c>
       <c r="AT257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45281,17 +45371,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45325,170 +45415,81 @@
         </is>
       </c>
       <c r="N258" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" t="n">
+        <v>1</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="n">
         <v>0</v>
       </c>
-      <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP258" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT258" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU258" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV258" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -45520,12 +45521,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45572,68 +45573,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45660,17 +45675,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45709,17 +45724,34 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="R260" t="n">
-        <v>0</v>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -45727,6 +45759,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -45739,12 +45829,12 @@
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
       <c r="AT260" t="n">
@@ -45752,47 +45842,47 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45819,17 +45909,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45868,165 +45958,614 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
+      <c r="AT261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="V261" t="inlineStr">
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="W261" t="inlineStr">
+      <c r="AT262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA262" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB262" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC262" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X261" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>Tyfoidfeber</t>
         </is>
       </c>
-      <c r="Y261" t="inlineStr">
+      <c r="Y263" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z261" t="inlineStr">
+      <c r="Z263" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA261" t="inlineStr">
+      <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB261" t="inlineStr">
+      <c r="AB263" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC261" t="inlineStr">
+      <c r="AC263" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD261" t="inlineStr">
+      <c r="AD263" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE261" t="inlineStr">
+      <c r="AE263" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF261" t="inlineStr">
+      <c r="AF263" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG261" t="inlineStr">
+      <c r="AG263" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH261" t="inlineStr">
+      <c r="AH263" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI261" t="inlineStr">
+      <c r="AI263" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ261" t="inlineStr">
+      <c r="AJ263" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK261" t="inlineStr">
+      <c r="AK263" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
         </is>
       </c>
-      <c r="AM261" t="inlineStr">
+      <c r="AM263" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN261" t="b">
+      <c r="AN263" t="b">
         <v>1</v>
       </c>
-      <c r="AO261" t="inlineStr">
+      <c r="AO263" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP261" t="inlineStr">
+      <c r="AP263" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ261" t="inlineStr">
+      <c r="AQ263" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS261" t="inlineStr">
+      <c r="AS263" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="AT261" t="n">
+      <c r="AT263" t="n">
         <v>1</v>
       </c>
-      <c r="AU261" t="inlineStr">
+      <c r="AU263" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV261" t="inlineStr">
+      <c r="AV263" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW261" t="inlineStr">
+      <c r="AW263" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX261" t="inlineStr">
+      <c r="AX263" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY261" t="inlineStr">
+      <c r="AY263" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ261" t="inlineStr">
+      <c r="AZ263" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA261" t="inlineStr">
+      <c r="BA263" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB261" t="inlineStr">
+      <c r="BB263" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC261" t="inlineStr">
+      <c r="BC263" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>4</v>
+      </c>
+      <c r="O264" t="n">
+        <v>4</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0.001146015253107754</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
+      <c r="AT264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV264" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA264" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB264" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC264" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46063,7 +46602,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -46146,7 +46685,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -46156,7 +46695,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -46176,7 +46715,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -46208,7 +46747,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -41744,13 +41744,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R237" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -46343,13 +46343,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -46956,6 +46956,151 @@
       <c r="BC266" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
+      <c r="AT267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB267" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC267" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46992,7 +47137,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -47075,7 +47220,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -47085,7 +47230,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -47137,7 +47282,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -42243,12 +42243,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42282,13 +42282,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O240" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R240" t="n">
-        <v>0.03737952171313338</v>
+        <v>0.03782520932943658</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -42322,7 +42322,7 @@
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT240" t="n">
@@ -42335,42 +42335,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42402,12 +42402,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -42441,29 +42441,29 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O241" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t>Tyfoidfeber</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="Y241" t="inlineStr">
@@ -42473,7 +42473,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -42488,7 +42488,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -42523,17 +42523,17 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
         </is>
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -42556,7 +42556,7 @@
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT241" t="n">
@@ -42569,42 +42569,42 @@
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42636,12 +42636,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -42675,81 +42675,95 @@
         </is>
       </c>
       <c r="N242" t="n">
+        <v>4</v>
+      </c>
+      <c r="O242" t="n">
+        <v>4</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT242" t="n">
         <v>1</v>
       </c>
-      <c r="O242" t="n">
-        <v>1</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO242" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP242" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
-      <c r="AT242" t="n">
-        <v>0</v>
-      </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42776,17 +42790,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -42811,7 +42825,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -42820,81 +42834,170 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN243" t="b">
+        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -42926,12 +43029,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -42956,7 +43059,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -42965,93 +43068,81 @@
         </is>
       </c>
       <c r="N244" t="n">
+        <v>1</v>
+      </c>
+      <c r="O244" t="n">
+        <v>1</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="n">
         <v>0</v>
       </c>
-      <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" t="n">
-        <v>0</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
-      <c r="AT244" t="n">
-        <v>2</v>
-      </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43078,17 +43169,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43127,168 +43218,76 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="P245" t="n">
+      <c r="R245" t="n">
         <v>0</v>
       </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43320,12 +43319,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -43350,7 +43349,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -43359,81 +43358,93 @@
         </is>
       </c>
       <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT246" t="n">
         <v>2</v>
       </c>
-      <c r="O246" t="n">
-        <v>2</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO246" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP246" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
-      <c r="AT246" t="n">
-        <v>0</v>
-      </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43460,7 +43471,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -43495,7 +43506,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -43504,26 +43515,106 @@
         </is>
       </c>
       <c r="N247" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
         <v>1</v>
-      </c>
-      <c r="O247" t="n">
-        <v>1</v>
-      </c>
-      <c r="P247" t="n">
-        <v>1</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
@@ -43617,17 +43708,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43661,173 +43752,81 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O248" t="n">
-        <v>1</v>
-      </c>
-      <c r="P248" t="n">
-        <v>1</v>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN248" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43859,12 +43858,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43889,7 +43888,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -43898,81 +43897,93 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P249" t="n">
+        <v>1</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43999,7 +44010,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -44034,7 +44045,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -44043,26 +44054,106 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
@@ -44156,17 +44247,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44205,168 +44296,76 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="P251" t="n">
+      <c r="R251" t="n">
         <v>0</v>
       </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44398,12 +44397,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44428,7 +44427,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -44437,81 +44436,93 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
         <v>2</v>
       </c>
-      <c r="O252" t="n">
-        <v>2</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO252" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP252" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr"/>
-      <c r="AT252" t="n">
-        <v>0</v>
-      </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44538,17 +44549,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44573,7 +44584,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -44587,76 +44598,168 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="R253" t="n">
+      <c r="P253" t="n">
         <v>0</v>
       </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44688,12 +44791,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44718,7 +44821,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44727,93 +44830,81 @@
         </is>
       </c>
       <c r="N254" t="n">
+        <v>2</v>
+      </c>
+      <c r="O254" t="n">
+        <v>2</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
+      <c r="AT254" t="n">
         <v>0</v>
       </c>
-      <c r="O254" t="n">
-        <v>0</v>
-      </c>
-      <c r="P254" t="n">
-        <v>0</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP254" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
-      <c r="AT254" t="n">
-        <v>2</v>
-      </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44840,17 +44931,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44889,168 +44980,76 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="P255" t="n">
+      <c r="R255" t="n">
         <v>0</v>
       </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45082,12 +45081,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45112,7 +45111,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -45121,81 +45120,93 @@
         </is>
       </c>
       <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
         <v>2</v>
       </c>
-      <c r="O256" t="n">
-        <v>2</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP256" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
-      <c r="AT256" t="n">
-        <v>0</v>
-      </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45222,17 +45233,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45257,7 +45268,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45266,81 +45277,173 @@
         </is>
       </c>
       <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
         <v>1</v>
       </c>
-      <c r="O257" t="n">
-        <v>1</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45372,12 +45475,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45402,7 +45505,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45411,93 +45514,81 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O258" t="n">
-        <v>1</v>
-      </c>
-      <c r="P258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R258" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45524,17 +45615,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45573,168 +45664,76 @@
       <c r="O259" t="n">
         <v>1</v>
       </c>
-      <c r="P259" t="n">
-        <v>1</v>
-      </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN259" t="b">
-        <v>1</v>
+      <c r="R259" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45766,12 +45765,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45796,12 +45795,12 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N260" t="n">
@@ -45810,76 +45809,88 @@
       <c r="O260" t="n">
         <v>1</v>
       </c>
+      <c r="P260" t="n">
+        <v>1</v>
+      </c>
       <c r="R260" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45906,17 +45917,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45941,37 +45952,115 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
-      </c>
-      <c r="R261" t="n">
-        <v>0</v>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P261" t="n">
+        <v>1</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
@@ -45980,65 +46069,65 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46065,17 +46154,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46109,170 +46198,81 @@
         </is>
       </c>
       <c r="N262" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" t="n">
+        <v>1</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
+      <c r="AT262" t="n">
         <v>0</v>
       </c>
-      <c r="O262" t="n">
-        <v>0</v>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN262" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO262" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP262" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT262" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU262" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV262" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46304,12 +46304,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46343,81 +46343,95 @@
         </is>
       </c>
       <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AT263" t="n">
         <v>1</v>
       </c>
-      <c r="O263" t="n">
-        <v>1</v>
-      </c>
-      <c r="R263" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP263" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
-      <c r="AT263" t="n">
-        <v>0</v>
-      </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46444,17 +46458,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46493,17 +46507,34 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="R264" t="n">
-        <v>0</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -46511,6 +46542,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
+        <v>1</v>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46523,12 +46612,12 @@
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
       <c r="AT264" t="n">
@@ -46536,47 +46625,47 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46603,17 +46692,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46647,170 +46736,81 @@
         </is>
       </c>
       <c r="N265" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" t="n">
+        <v>1</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
+      <c r="AT265" t="n">
         <v>0</v>
       </c>
-      <c r="O265" t="n">
-        <v>0</v>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN265" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP265" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT265" t="n">
-        <v>1</v>
-      </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -46842,12 +46842,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46872,7 +46872,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -46881,81 +46881,95 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>0.001146015253107754</v>
+        <v>0</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46982,17 +46996,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -47017,7 +47031,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -47031,74 +47045,453 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="R267" t="n">
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB267" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC267" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>4</v>
+      </c>
+      <c r="O268" t="n">
+        <v>4</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0.001146015253107754</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
+      <c r="AT268" t="n">
         <v>0</v>
       </c>
-      <c r="S267" t="inlineStr">
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV268" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA268" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB268" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC268" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO267" t="inlineStr">
+      <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP267" t="inlineStr">
+      <c r="AP269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR267" t="inlineStr">
+      <c r="AR269" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS267" t="inlineStr"/>
-      <c r="AT267" t="n">
+      <c r="AS269" t="inlineStr"/>
+      <c r="AT269" t="n">
         <v>0</v>
       </c>
-      <c r="AU267" t="inlineStr">
+      <c r="AU269" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV267" t="inlineStr">
+      <c r="AV269" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW267" t="inlineStr">
+      <c r="AW269" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX267" t="inlineStr">
+      <c r="AX269" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY267" t="inlineStr">
+      <c r="AY269" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ267" t="inlineStr">
+      <c r="AZ269" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA267" t="inlineStr">
+      <c r="BA269" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB267" t="inlineStr">
+      <c r="BB269" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC267" t="inlineStr">
+      <c r="BC269" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -47220,7 +47613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
@@ -47230,7 +47623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -47250,7 +47643,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -47282,7 +47675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -46881,13 +46881,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -47040,10 +47040,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -46736,13 +46736,13 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -47494,6 +47494,545 @@
       <c r="BC269" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" t="n">
+        <v>2</v>
+      </c>
+      <c r="P270" t="n">
+        <v>2</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>2</v>
+      </c>
+      <c r="O271" t="n">
+        <v>2</v>
+      </c>
+      <c r="P271" t="n">
+        <v>2</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" t="n">
+        <v>1</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
+      <c r="AT272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47530,7 +48069,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -47613,7 +48152,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -47623,7 +48162,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -47643,7 +48182,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -47675,7 +48214,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -41744,13 +41744,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R237" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -40354,13 +40354,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O228" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R228" t="n">
-        <v>0.03305530637567811</v>
+        <v>0.02938249455615832</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -41705,12 +41705,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -41744,13 +41744,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R237" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -41783,42 +41783,42 @@
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -41850,12 +41850,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -41895,89 +41895,75 @@
         <v>1</v>
       </c>
       <c r="R238" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA238" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -42004,7 +41990,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -42053,98 +42039,23 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
+      <c r="R239" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U239" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN239" t="b">
-        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
@@ -42238,17 +42149,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42282,22 +42193,39 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O240" t="n">
-        <v>2</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0.03782520932943658</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -42305,6 +42233,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN240" t="b">
+        <v>1</v>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -42322,7 +42308,7 @@
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AT240" t="n">
@@ -42335,42 +42321,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42397,7 +42383,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -42446,98 +42432,23 @@
       <c r="O241" t="n">
         <v>2</v>
       </c>
+      <c r="R241" t="n">
+        <v>0.03782520932943658</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Typhoid fever</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -42631,17 +42542,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -42675,22 +42586,39 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O242" t="n">
-        <v>4</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.03737952171313338</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -42698,6 +42626,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -42715,7 +42701,7 @@
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -42728,42 +42714,42 @@
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42790,7 +42776,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -42839,98 +42825,23 @@
       <c r="O243" t="n">
         <v>4</v>
       </c>
+      <c r="R243" t="n">
+        <v>0.03737952171313338</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U243" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TYPHOID</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -43024,17 +42935,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -43068,81 +42979,170 @@
         </is>
       </c>
       <c r="N244" t="n">
+        <v>4</v>
+      </c>
+      <c r="O244" t="n">
+        <v>4</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
         <v>1</v>
       </c>
-      <c r="O244" t="n">
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT244" t="n">
         <v>1</v>
       </c>
-      <c r="R244" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
-      <c r="AT244" t="n">
-        <v>0</v>
-      </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43174,12 +43174,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43204,7 +43204,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -43213,13 +43213,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -43252,42 +43252,42 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -43319,12 +43319,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -43363,9 +43363,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="P246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -43374,77 +43371,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -43471,7 +43459,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -43523,98 +43511,18 @@
       <c r="P247" t="n">
         <v>0</v>
       </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R247" t="n">
+        <v>0</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN247" t="b">
-        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
@@ -43708,17 +43616,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -43743,7 +43651,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -43752,81 +43660,173 @@
         </is>
       </c>
       <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT248" t="n">
         <v>2</v>
       </c>
-      <c r="O248" t="n">
-        <v>2</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO248" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP248" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
-      <c r="AT248" t="n">
-        <v>0</v>
-      </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -43858,12 +43858,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43897,93 +43897,81 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O249" t="n">
-        <v>1</v>
-      </c>
-      <c r="P249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R249" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ249" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44010,7 +43998,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -44062,98 +44050,18 @@
       <c r="P250" t="n">
         <v>1</v>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R250" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN250" t="b">
-        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
@@ -44247,17 +44155,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44282,7 +44190,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -44291,81 +44199,173 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P251" t="n">
+        <v>1</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44397,12 +44397,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44441,9 +44441,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="P252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -44452,77 +44449,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44549,7 +44537,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -44601,98 +44589,18 @@
       <c r="P253" t="n">
         <v>0</v>
       </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -44786,17 +44694,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44821,7 +44729,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -44830,81 +44738,173 @@
         </is>
       </c>
       <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
         <v>2</v>
       </c>
-      <c r="O254" t="n">
-        <v>2</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP254" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
-      <c r="AT254" t="n">
-        <v>0</v>
-      </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44936,12 +44936,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44966,7 +44966,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -44975,13 +44975,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -45014,42 +45014,42 @@
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45081,12 +45081,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45125,9 +45125,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="P256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -45136,77 +45133,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45233,7 +45221,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -45285,98 +45273,18 @@
       <c r="P257" t="n">
         <v>0</v>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -45470,17 +45378,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45505,7 +45413,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45514,81 +45422,173 @@
         </is>
       </c>
       <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT258" t="n">
         <v>2</v>
       </c>
-      <c r="O258" t="n">
-        <v>2</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP258" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
-      <c r="AT258" t="n">
-        <v>0</v>
-      </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45620,12 +45620,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45659,13 +45659,13 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R259" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -45698,42 +45698,42 @@
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45765,12 +45765,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45809,88 +45809,76 @@
       <c r="O260" t="n">
         <v>1</v>
       </c>
-      <c r="P260" t="n">
-        <v>1</v>
-      </c>
       <c r="R260" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45917,7 +45905,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -45969,98 +45957,18 @@
       <c r="P261" t="n">
         <v>1</v>
       </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R261" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD261" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE261" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF261" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG261" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK261" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM261" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN261" t="b">
-        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
@@ -46154,17 +46062,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46189,12 +46097,12 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N262" t="n">
@@ -46203,76 +46111,168 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
-      <c r="R262" t="n">
-        <v>0.00367281181951979</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P262" t="n">
+        <v>1</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46304,12 +46304,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46343,95 +46343,81 @@
         </is>
       </c>
       <c r="N263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="n">
+        <v>1</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
+      <c r="AT263" t="n">
         <v>0</v>
       </c>
-      <c r="O263" t="n">
-        <v>0</v>
-      </c>
-      <c r="R263" t="n">
-        <v>0</v>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP263" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT263" t="n">
-        <v>1</v>
-      </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46458,7 +46444,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -46507,98 +46493,23 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U264" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN264" t="b">
-        <v>1</v>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
@@ -46692,17 +46603,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46741,76 +46652,165 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="R265" t="n">
-        <v>0</v>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46842,12 +46842,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46881,95 +46881,81 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -46996,7 +46982,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -47045,98 +47031,23 @@
       <c r="O267" t="n">
         <v>1</v>
       </c>
+      <c r="R267" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U267" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN267" t="b">
-        <v>1</v>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
@@ -47230,17 +47141,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47265,7 +47176,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -47274,81 +47185,170 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O268" t="n">
-        <v>4</v>
-      </c>
-      <c r="R268" t="n">
-        <v>0.001146015253107754</v>
-      </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN268" t="b">
+        <v>1</v>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -47380,12 +47380,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47410,7 +47410,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -47419,13 +47419,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>0.001146015253107754</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -47458,42 +47458,42 @@
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47525,12 +47525,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47564,93 +47564,81 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O270" t="n">
-        <v>2</v>
-      </c>
-      <c r="P270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>0.03386531510194095</v>
+        <v>0</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47677,7 +47665,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -47729,98 +47717,18 @@
       <c r="P271" t="n">
         <v>2</v>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R271" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN271" t="b">
-        <v>1</v>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
@@ -47914,123 +47822,1044 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>2</v>
+      </c>
+      <c r="O272" t="n">
+        <v>2</v>
+      </c>
+      <c r="P272" t="n">
+        <v>2</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G273" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>D124</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>Typhoid fever</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
         <is>
           <t>伤寒</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="K273" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
+      <c r="L273" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N272" t="n">
+      <c r="N273" t="n">
         <v>1</v>
       </c>
-      <c r="O272" t="n">
+      <c r="O273" t="n">
         <v>1</v>
       </c>
-      <c r="R272" t="n">
+      <c r="R273" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S272" t="inlineStr">
+      <c r="S273" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO272" t="inlineStr">
+      <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP272" t="inlineStr">
+      <c r="AP273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR272" t="inlineStr">
+      <c r="AR273" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS272" t="inlineStr"/>
-      <c r="AT272" t="n">
+      <c r="AS273" t="inlineStr"/>
+      <c r="AT273" t="n">
         <v>0</v>
       </c>
-      <c r="AU272" t="inlineStr">
+      <c r="AU273" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV272" t="inlineStr">
+      <c r="AV273" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW272" t="inlineStr">
+      <c r="AW273" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX272" t="inlineStr">
+      <c r="AX273" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY272" t="inlineStr">
+      <c r="AY273" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ272" t="inlineStr">
+      <c r="AZ273" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA272" t="inlineStr">
+      <c r="BA273" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB272" t="inlineStr">
+      <c r="BB273" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC272" t="inlineStr">
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>1</v>
+      </c>
+      <c r="O274" t="n">
+        <v>1</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
+      <c r="AT274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>1</v>
+      </c>
+      <c r="O275" t="n">
+        <v>1</v>
+      </c>
+      <c r="P275" t="n">
+        <v>1</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" t="n">
+        <v>1</v>
+      </c>
+      <c r="P276" t="n">
+        <v>1</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>6</v>
+      </c>
+      <c r="O277" t="n">
+        <v>6</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
+      <c r="AT277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -48069,7 +48898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -48152,7 +48981,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -48162,7 +48991,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
@@ -48182,7 +49011,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -48214,7 +49043,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -37763,16 +37763,16 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -37920,13 +37920,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
@@ -38447,16 +38447,16 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R217" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -38604,13 +38604,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -39131,16 +39131,16 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R221" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -39288,13 +39288,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
@@ -39960,16 +39960,16 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -40117,13 +40117,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -41889,13 +41889,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R238" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -43503,16 +43503,16 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -43660,13 +43660,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -44042,16 +44042,16 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R250" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -44199,13 +44199,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -44581,16 +44581,16 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -44738,13 +44738,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
@@ -45949,16 +45949,16 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R261" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -46106,13 +46106,13 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -46343,13 +46343,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O263" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R263" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -46881,13 +46881,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -47709,16 +47709,16 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R271" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -47866,13 +47866,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
@@ -48862,6 +48862,1228 @@
       <c r="BC277" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
+      <c r="AT278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>2</v>
+      </c>
+      <c r="O279" t="n">
+        <v>2</v>
+      </c>
+      <c r="P279" t="n">
+        <v>2</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>2</v>
+      </c>
+      <c r="O280" t="n">
+        <v>2</v>
+      </c>
+      <c r="P280" t="n">
+        <v>2</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN280" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" t="n">
+        <v>1</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr"/>
+      <c r="AT281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48898,7 +50120,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -48981,7 +50203,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -48991,7 +50213,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -49011,7 +50233,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -49043,7 +50265,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -46343,13 +46343,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O263" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R263" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -30557,7 +30557,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -36400,7 +36400,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -47277,7 +47277,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN268" t="b">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -74834,13 +74834,13 @@
         </is>
       </c>
       <c r="N459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R459" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S459" t="inlineStr">
         <is>
@@ -79723,7 +79723,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -73127,13 +73127,13 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O448" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R448" t="n">
-        <v>0.02570968273663853</v>
+        <v>0.02938249455615832</v>
       </c>
       <c r="S448" t="inlineStr">
         <is>
@@ -79542,6 +79542,151 @@
       <c r="BC485" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N486" t="n">
+        <v>0</v>
+      </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
+      <c r="R486" t="n">
+        <v>0</v>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO486" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP486" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR486" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS486" t="inlineStr"/>
+      <c r="AT486" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU486" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV486" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW486" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX486" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY486" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA486" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB486" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC486" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -79578,7 +79723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -79661,7 +79806,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10">
@@ -79671,7 +79816,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -79723,7 +79868,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -10239,9 +10239,6 @@
       <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -20570,9 +20567,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -21265,9 +21259,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -29349,9 +29340,6 @@
       <c r="O183" t="n">
         <v>1</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -30739,9 +30727,6 @@
       <c r="O191" t="n">
         <v>2</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -31434,9 +31419,6 @@
       <c r="O195" t="n">
         <v>1</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -39671,9 +39653,6 @@
       <c r="O248" t="n">
         <v>3</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -41756,9 +41735,6 @@
       <c r="O260" t="n">
         <v>3</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -50820,9 +50796,6 @@
       <c r="O318" t="n">
         <v>1</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -51515,9 +51488,6 @@
       <c r="O322" t="n">
         <v>1</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -52210,9 +52180,6 @@
       <c r="O326" t="n">
         <v>1</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -62980,13 +62947,13 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R389" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S389" t="inlineStr">
         <is>
@@ -63139,10 +63106,10 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O390" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U390" t="inlineStr">
         <is>
@@ -79687,6 +79654,156 @@
       <c r="BC486" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N487" t="n">
+        <v>2</v>
+      </c>
+      <c r="O487" t="n">
+        <v>2</v>
+      </c>
+      <c r="R487" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA487" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO487" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP487" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR487" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS487" t="inlineStr"/>
+      <c r="AT487" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU487" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV487" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW487" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX487" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY487" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA487" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB487" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC487" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79723,7 +79840,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -79806,7 +79923,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10">
@@ -79816,7 +79933,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11">
@@ -79868,7 +79985,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="16">
